--- a/naver-place-crawler/results_health/사하구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/사하구_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>인더짐 헬스&amp;기구필라테스&amp;요가&amp;PT 괴정점</t>
+          <t>헬스버디짐 줌바&amp;요가&amp;필라테스 장림점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>inthegym01@naver.com</t>
+          <t>jlfitness_j@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1358-6699</t>
+          <t>0507-1310-1470</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 사하로186번길 6 하정빌딩</t>
+          <t>부산 사하구 장림번영로 50 상가 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/inthegym01</t>
+          <t>https://www.instagram.com/healthbuddy_janglim?igsh=ZnZmcW54dDNyNnBh</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,15 +601,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4011x</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>591</v>
+        <v>1225</v>
       </c>
       <c r="Q2" t="n">
-        <v>712</v>
+        <v>622</v>
       </c>
       <c r="R2" t="n">
-        <v>1303</v>
+        <v>1847</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1419272513</t>
+          <t>1315960121</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1419272513</t>
+          <t>https://m.place.naver.com/place/1315960121</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>헬스보이짐 &amp;WeWe필라테스&amp;요가당리점</t>
+          <t>하파휘트니스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>healthboy_dangri@naver.com</t>
+          <t>kdh31307o@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1383-9590</t>
+          <t>051-293-3000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 381 1~3층</t>
+          <t>부산광역시 사하구 낙동대로 474 대하빌딩 7층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/saN4gz5h</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -706,22 +710,22 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>98</v>
+        <v>302</v>
       </c>
       <c r="Q3" t="n">
-        <v>172</v>
+        <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,24 +734,24 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1076645615</t>
+          <t>36771036</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1076645615</t>
+          <t>https://m.place.naver.com/place/36771036</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -809,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="Q4" t="n">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="R4" t="n">
-        <v>681</v>
+        <v>715</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,41 +838,41 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>헬스보이짐 하단점 PT&amp;헬스</t>
+          <t>인더짐 헬스&amp;기구필라테스&amp;요가&amp;PT 괴정점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>healthboy34@naver.com</t>
+          <t>inthegym01@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1489-5775</t>
+          <t>0507-1358-6699</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동남로 1403 2층</t>
+          <t>부산광역시 사하구 사하로186번길 6 하정빌딩</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboy34</t>
+          <t>https://blog.naver.com/inthegym01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -903,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="Q5" t="n">
-        <v>629</v>
+        <v>720</v>
       </c>
       <c r="R5" t="n">
-        <v>1215</v>
+        <v>1319</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +922,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1791255308</t>
+          <t>1419272513</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1791255308</t>
+          <t>https://m.place.naver.com/place/1419272513</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>빅스짐 하단점 헬스 PT</t>
+          <t>24시 트렌드핏 피트니스 하단점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bigsgym20@naver.com</t>
+          <t>gkeks66@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1357-6662</t>
+          <t>0507-1303-2924</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로457번길 5 301호</t>
+          <t>부산광역시 사하구 낙동대로 475 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_hadan</t>
+          <t>https://blog.naver.com/gkeks66</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,7 +981,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -997,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1156</v>
+        <v>1552</v>
       </c>
       <c r="Q6" t="n">
-        <v>421</v>
+        <v>480</v>
       </c>
       <c r="R6" t="n">
-        <v>1577</v>
+        <v>2032</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1016,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1652983472</t>
+          <t>1354278156</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1652983472</t>
+          <t>https://m.place.naver.com/place/1354278156</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피트니스 넘버원 헬스&amp;PT 괴정점</t>
+          <t>헬스보이짐 &amp;WeWe필라테스&amp;요가당리점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fitnessgymseung@naver.com</t>
+          <t>healthboy_dangri@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1388-7941</t>
+          <t>0507-1383-9590</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 203 엔스타상가 210,211호</t>
+          <t>부산광역시 사하구 낙동대로 381 1~3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://open.kakao.com/me/gymseung</t>
+          <t>https://open.kakao.com/o/saN4gz5h</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1095,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="Q7" t="n">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="R7" t="n">
-        <v>314</v>
+        <v>278</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1110,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1519532322</t>
+          <t>1076645615</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1519532322</t>
+          <t>https://m.place.naver.com/place/1076645615</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1128,34 +1132,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GYM 루소킹 괴정점 헬스&amp;PT</t>
+          <t>피트니스 넘버원 헬스&amp;PT 괴정점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gym_rusoking@naver.com</t>
+          <t>fitnessgymseung@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1368-4733</t>
+          <t>0507-1388-7941</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로216번길 3 신화프라자 1층 괴정역2번출구 도보30초</t>
+          <t>부산광역시 사하구 낙동대로 203 엔스타상가 210,211호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_UxdxbUG/friend</t>
+          <t>http://open.kakao.com/me/gymseung</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1181,17 +1185,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>488</v>
+        <v>115</v>
       </c>
       <c r="Q8" t="n">
-        <v>421</v>
+        <v>204</v>
       </c>
       <c r="R8" t="n">
-        <v>909</v>
+        <v>319</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,56 +1204,56 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>37438088</t>
+          <t>1519532322</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37438088</t>
+          <t>https://m.place.naver.com/place/1519532322</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>헬스버디짐 줌바&amp;요가&amp;필라테스 장림점</t>
+          <t>스카이짐24H &amp; 기구필라테스 &amp; GDR골프</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jlfitness_j@naver.com</t>
+          <t>skygym21@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1310-1470</t>
+          <t>0507-1473-5661</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 장림번영로 50 상가 2층</t>
+          <t>부산광역시 사하구 장평로 440 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healthbuddy_janglim?igsh=ZnZmcW54dDNyNnBh</t>
+          <t>http://www.skygym.co.kr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1259,7 +1263,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,17 +1279,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1195</v>
+        <v>2079</v>
       </c>
       <c r="Q9" t="n">
-        <v>615</v>
+        <v>140</v>
       </c>
       <c r="R9" t="n">
-        <v>1810</v>
+        <v>2219</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1298,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1315960121</t>
+          <t>1429668350</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1315960121</t>
+          <t>https://m.place.naver.com/place/1429668350</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>지존 헬스&amp;피트니스</t>
+          <t>빅스짐 하단점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>zzonept@naver.com</t>
+          <t>bigsgym20@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>051-266-2660</t>
+          <t>0507-1357-6662</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 다대로 207 세정아울렛 1,2,3층 (상담은 3층 카운터)</t>
+          <t>부산광역시 사하구 낙동대로457번길 5 301호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/zzonept</t>
+          <t>https://www.instagram.com/bigsgym_hadan</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1357,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1369,17 +1373,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>161</v>
+        <v>1154</v>
       </c>
       <c r="Q10" t="n">
-        <v>93</v>
+        <v>431</v>
       </c>
       <c r="R10" t="n">
-        <v>254</v>
+        <v>1585</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,1047 +1392,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>38563721</t>
+          <t>1652983472</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38563721</t>
+          <t>https://m.place.naver.com/place/1652983472</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>허그짐 다대포 낫개점 헬스&amp;PT</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>huggymdadaepo9704@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>부산광역시 사하구 다송로84번길 52 2, 3층</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/huggymdadaepo9704</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>385</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>346</v>
-      </c>
-      <c r="R11" t="n">
-        <v>731</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1095357843</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1095357843</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>워너짐 헬스&amp;PT 하단점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>wannagym87@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1477-1511</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>부산광역시 사하구 하신번영로 352 우리마트 2층(하단동)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/wannagym11_hadan</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>395</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>51</v>
-      </c>
-      <c r="R12" t="n">
-        <v>446</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1180864218</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1180864218</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>동아기능성운동트레이닝센터</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>dfet0226@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1494-7910</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>부산광역시 사하구 낙동대로550번길 37 예술체육대학1관 106호</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/dfet0226</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>161</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>297</v>
-      </c>
-      <c r="R13" t="n">
-        <v>458</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1619665911</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1619665911</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>24시 트렌드핏 피트니스 하단점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>gkeks66@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1303-2924</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>부산광역시 사하구 낙동대로 475 2층</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/gkeks66</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1547</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>535</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2082</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1354278156</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1354278156</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>올짐 피트니스 &amp; 사우나 대티점</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>allgym_daeti@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1384-8306</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>부산광역시 사하구 낙동대로 137 대티역 스마트W 상가 1층 올짐 휘트니스 &amp; 사우나</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/allgym_daeti</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>292</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>691</v>
-      </c>
-      <c r="R15" t="n">
-        <v>983</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1698150913</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1698150913</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>에이토탈피트니스</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>sinby1987@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1433-0551</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>부산광역시 사하구 사하로 182 아델하임 3층</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/sinby1987</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>138</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>411</v>
-      </c>
-      <c r="R16" t="n">
-        <v>549</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1164084833</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1164084833</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>코치엔짐</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>iron0377@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1386-9682</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>부산광역시 사하구 다송로72번길 80 라브랜드 4층</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/iron0377</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>545</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>198</v>
-      </c>
-      <c r="R17" t="n">
-        <v>743</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1524946927</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1524946927</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>GO피트니스&amp;대기구필라테스 괴정점</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>gofitness_gj@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1402-0240</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>부산광역시 사하구 사하로 200 형지스퀘어 빌딩 7층, 8층</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/gofit_goejeong/</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>240</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>451</v>
-      </c>
-      <c r="R18" t="n">
-        <v>691</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>31681303</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/31681303</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>더케이피트니스 롯데마트사하</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>thekfitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1334-1844</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>부산광역시 사하구 을숙도대로 610 롯데마트 사하점 4층</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/the.k_fitness_saha</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>163</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>314</v>
-      </c>
-      <c r="R19" t="n">
-        <v>477</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1183759558</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1183759558</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>스카이짐24H &amp; 기구필라테스 &amp; GDR골프</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>skygym21@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1473-5661</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>부산광역시 사하구 장평로 440 5층</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>http://www.skygym.co.kr</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>2075</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>136</v>
-      </c>
-      <c r="R20" t="n">
-        <v>2211</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1429668350</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1429668350</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>머슬팩토리 신평점</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>musclefactory_@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1364-8147</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>부산광역시 사하구 하신중앙로 176 5층</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/musclefactory_</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>56</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>43</v>
-      </c>
-      <c r="R21" t="n">
-        <v>99</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1102814447</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1102814447</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/사하구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/사하구_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>헬스버디짐 줌바&amp;요가&amp;필라테스 장림점</t>
+          <t>인더짐 헬스&amp;기구필라테스&amp;요가&amp;PT 괴정점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jlfitness_j@naver.com</t>
+          <t>inthegym01@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1310-1470</t>
+          <t>0507-1358-6699</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 사하구 장림번영로 50 상가 2층</t>
+          <t>부산광역시 사하구 사하로186번길 6 하정빌딩</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/healthbuddy_janglim?igsh=ZnZmcW54dDNyNnBh</t>
+          <t>https://blog.naver.com/inthegym01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,19 +601,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4011x</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1225</v>
+        <v>600</v>
       </c>
       <c r="Q2" t="n">
-        <v>622</v>
+        <v>721</v>
       </c>
       <c r="R2" t="n">
-        <v>1847</v>
+        <v>1321</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1315960121</t>
+          <t>1419272513</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1315960121</t>
+          <t>https://m.place.naver.com/place/1419272513</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>하파휘트니스</t>
+          <t>헬스버디짐 줌바&amp;요가&amp;필라테스 장림점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>kdh31307o@naver.com</t>
+          <t>jlfitness_j@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>051-293-3000</t>
+          <t>0507-1310-1470</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 474 대하빌딩 7층</t>
+          <t>부산 사하구 장림번영로 50 상가 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/healthbuddy_janglim?igsh=ZnZmcW54dDNyNnBh</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -704,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4011x</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,17 +715,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>302</v>
+        <v>1230</v>
       </c>
       <c r="Q3" t="n">
-        <v>32</v>
+        <v>623</v>
       </c>
       <c r="R3" t="n">
-        <v>334</v>
+        <v>1853</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,17 +734,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>36771036</t>
+          <t>1315960121</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36771036</t>
+          <t>https://m.place.naver.com/place/1315960121</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -756,29 +756,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>404피트니스 헬스&amp;PT 하단점</t>
+          <t>하파휘트니스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>404fitnesshadan@naver.com</t>
+          <t>kdh31307o@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1395-4026</t>
+          <t>051-293-3000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로 487 4층</t>
+          <t>부산 사하구 낙동대로 474 대하빌딩 7층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/404_fitness_hadan/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -804,22 +804,22 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>424</v>
+        <v>302</v>
       </c>
       <c r="Q4" t="n">
-        <v>291</v>
+        <v>32</v>
       </c>
       <c r="R4" t="n">
-        <v>715</v>
+        <v>334</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,17 +828,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1669341529</t>
+          <t>36771036</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1669341529</t>
+          <t>https://m.place.naver.com/place/36771036</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -850,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>인더짐 헬스&amp;기구필라테스&amp;요가&amp;PT 괴정점</t>
+          <t>404피트니스 헬스&amp;PT 하단점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>inthegym01@naver.com</t>
+          <t>404fitnesshadan@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1358-6699</t>
+          <t>0507-1395-4026</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 사하로186번길 6 하정빌딩</t>
+          <t>부산광역시 사하구 낙동대로 487 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/inthegym01</t>
+          <t>https://www.instagram.com/404_fitness_hadan/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -898,7 +898,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -907,14 +907,14 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>599</v>
+        <v>429</v>
       </c>
       <c r="Q5" t="n">
+        <v>291</v>
+      </c>
+      <c r="R5" t="n">
         <v>720</v>
       </c>
-      <c r="R5" t="n">
-        <v>1319</v>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
           <t>X</t>
@@ -922,17 +922,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1419272513</t>
+          <t>1669341529</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1419272513</t>
+          <t>https://m.place.naver.com/place/1669341529</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="Q6" t="n">
         <v>480</v>
       </c>
       <c r="R6" t="n">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1098,10 +1098,10 @@
         <v>99</v>
       </c>
       <c r="Q7" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="R7" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 장평로 440 5층</t>
+          <t>부산 사하구 장평로 440 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1268,10 +1268,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wqbu4w7</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1286,10 +1290,10 @@
         <v>2079</v>
       </c>
       <c r="Q9" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="R9" t="n">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1308,7 +1312,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1377,10 +1381,10 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="Q10" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="R10" t="n">
         <v>1585</v>
@@ -1402,7 +1406,105 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>온유어짐PT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>cksah99@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1354-4205</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>부산 사하구 다대동 1628</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w15a2ii</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>9</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1770796114</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1770796114</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
